--- a/output/2026-09-02_17_Italia_Abruzzo_Depolverazione_Trattamento_aria.xlsx
+++ b/output/2026-09-02_17_Italia_Abruzzo_Depolverazione_Trattamento_aria.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Vendita e assistenza aspiratori industriali, idropulitrici, compressori, macchine per pulizia industriale. Verificato tramite fonti terze indipendenti (WebSearch, WebFetch bloccato da proxy).</t>
+          <t>Vendita e assistenza aspiratori industriali, idropulitrici, compressori, macchine per pulizia industriale. Verificato tramite fonti terze indipendenti (WebSearch, WebFetch bloccato da proxy). [DUPLICATO — vedi anche: 2026-09-02_00_Italia_Abruzzo_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -536,10 +536,9 @@
           <t>0871 561812 / 0871 552290</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Forniture industriali: aspiratori industriali con filtri HEPA per trucioli/polveri/liquidi, compressori, pneumatica/oleodinamica. Email non reperibile pubblicamente.</t>
+          <t>Forniture industriali: aspiratori industriali con filtri HEPA per trucioli/polveri/liquidi, compressori, pneumatica/oleodinamica. Email non reperibile pubblicamente. [DUPLICATO — vedi anche: 2026-09-02_00_Italia_Abruzzo_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -574,10 +573,9 @@
           <t>085 4684090 / 348 7012722</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Vendita e noleggio macchinari pulizia industriale, aspiratori professionali per polveri e liquidi. Email non reperibile pubblicamente.</t>
+          <t>Vendita e noleggio macchinari pulizia industriale, aspiratori professionali per polveri e liquidi. Email non reperibile pubblicamente. [DUPLICATO — vedi anche: 2026-08-31_21_Italia_Liguria_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -612,10 +610,9 @@
           <t>0863 509227 / 3772002391</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Vendita e noleggio macchinari pulizia industriale, aspiratori di liquidi e polveri, attrezzature per pulizia. Email non reperibile pubblicamente.</t>
+          <t>Vendita e noleggio macchinari pulizia industriale, aspiratori di liquidi e polveri, attrezzature per pulizia. Email non reperibile pubblicamente. [DUPLICATO — vedi anche: 2026-09-02_00_Italia_Abruzzo_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
